--- a/Rapid Cortex Internal Docs/Archive/Rapid_Cortex_Pricing_Complete.xlsx
+++ b/Rapid Cortex Internal Docs/Archive/Rapid_Cortex_Pricing_Complete.xlsx
@@ -6,9 +6,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-29480" yWindow="1860" windowWidth="28040" windowHeight="17440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rapid Cortex Essential" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rapid Cortex Professional" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rapid Cortex Command" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NexCort iQ Essential" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NexCort iQ Professional" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NexCort iQ Command" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enterprise_Statewide" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD Integration" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supervisor_QA" sheetId="6" state="visible" r:id="rId6"/>
@@ -623,14 +623,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RAPID CORTEX ESSENTIAL</t>
+          <t>NEXCORT IQ ESSENTIAL</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -3356,14 +3356,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RAPID CORTEX PROFESSIONAL</t>
+          <t>NEXCORT IQ PROFESSIONAL</t>
         </is>
       </c>
     </row>
@@ -3752,14 +3752,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RAPID CORTEX COMMAND</t>
+          <t>NEXCORT IQ COMMAND</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAPID CORTEX — INTERNAL PRICING MODEL</t>
+          <t>NEXCORT IQ — INTERNAL PRICING MODEL</t>
         </is>
       </c>
     </row>
